--- a/02-Test-Cases/Udemy_Search_TestCases.xlsx
+++ b/02-Test-Cases/Udemy_Search_TestCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ql3ql\Desktop\Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ql3ql\Desktop\resume\Review\Test-Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B985874C-BAA9-4D0E-AB1E-C67640631993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAA7E6B-5565-448A-994C-78F21E025CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{846BE328-7656-4A1D-8791-7828F6119A26}"/>
   </bookViews>
@@ -986,14 +986,11 @@
     <xf numFmtId="176" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1001,6 +998,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1397,7 +1397,7 @@
     <tabColor rgb="FF6AA84F"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -1406,10 +1406,9 @@
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="14" t="s">
         <v>185</v>
       </c>
@@ -1428,9 +1427,8 @@
       <c r="F1" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" ht="13.2">
+    </row>
+    <row r="2" spans="1:6" ht="13.2">
       <c r="A2" s="12" t="s">
         <v>99</v>
       </c>
@@ -1439,9 +1437,8 @@
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6">
+    </row>
+    <row r="3" spans="1:6" ht="15.6">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -1454,25 +1451,24 @@
       <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" ht="13.2">
+    </row>
+    <row r="4" spans="1:6" ht="13.2">
       <c r="A4" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="13.2">
+    <row r="5" spans="1:6" ht="13.2">
       <c r="A5" s="4" t="s">
         <v>176</v>
       </c>
@@ -1484,7 +1480,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="13.2">
+    <row r="6" spans="1:6" ht="13.2">
       <c r="A6" s="4" t="s">
         <v>175</v>
       </c>
@@ -1496,7 +1492,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="15.6">
+    <row r="7" spans="1:6" ht="15.6">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -1509,25 +1505,24 @@
       <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="13.2">
+    </row>
+    <row r="8" spans="1:6" ht="13.2">
       <c r="A8" s="4" t="s">
         <v>172</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="13.2">
+    <row r="9" spans="1:6" ht="13.2">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -1539,7 +1534,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="13.2">
+    <row r="10" spans="1:6" ht="13.2">
       <c r="A10" s="4" t="s">
         <v>169</v>
       </c>
@@ -1551,7 +1546,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="26.4">
+    <row r="11" spans="1:6" ht="26.4">
       <c r="A11" s="4" t="s">
         <v>168</v>
       </c>
@@ -1563,7 +1558,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="15.6">
+    <row r="12" spans="1:6" ht="15.6">
       <c r="A12" s="8">
         <v>3</v>
       </c>
@@ -1576,25 +1571,24 @@
       <c r="F12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="13.2">
+    </row>
+    <row r="13" spans="1:6" ht="13.2">
       <c r="A13" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="13.2">
+    <row r="14" spans="1:6" ht="13.2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -1606,7 +1600,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="13.2">
+    <row r="15" spans="1:6" ht="13.2">
       <c r="A15" s="4" t="s">
         <v>161</v>
       </c>
@@ -1618,7 +1612,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="26.4">
+    <row r="16" spans="1:6" ht="26.4">
       <c r="A16" s="4" t="s">
         <v>159</v>
       </c>
@@ -1630,7 +1624,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="26.4">
+    <row r="17" spans="1:6" ht="26.4">
       <c r="A17" s="4" t="s">
         <v>157</v>
       </c>
@@ -1642,7 +1636,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15.6">
+    <row r="18" spans="1:6" ht="15.6">
       <c r="A18" s="8">
         <v>4</v>
       </c>
@@ -1653,27 +1647,26 @@
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13.2">
       <c r="A19" s="4" t="s">
         <v>154</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="26.4">
+    <row r="20" spans="1:6" ht="26.4">
       <c r="A20" s="4" t="s">
         <v>152</v>
       </c>
@@ -1685,7 +1678,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="13.2">
+    <row r="21" spans="1:6" ht="13.2">
       <c r="A21" s="4" t="s">
         <v>150</v>
       </c>
@@ -1697,7 +1690,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="15.6">
+    <row r="22" spans="1:6" ht="15.6">
       <c r="A22" s="8">
         <v>5</v>
       </c>
@@ -1708,27 +1701,26 @@
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="13.2">
       <c r="A23" s="4" t="s">
         <v>148</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:7" ht="26.4">
+    <row r="24" spans="1:6" ht="26.4">
       <c r="A24" s="4" t="s">
         <v>146</v>
       </c>
@@ -1740,7 +1732,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="13.2">
+    <row r="25" spans="1:6" ht="13.2">
       <c r="A25" s="4" t="s">
         <v>144</v>
       </c>
@@ -1752,7 +1744,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:6" ht="15.6">
       <c r="A26" s="8">
         <v>6</v>
       </c>
@@ -1763,27 +1755,26 @@
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="13.2">
       <c r="A27" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="26.4">
+    <row r="28" spans="1:6" ht="26.4">
       <c r="A28" s="4" t="s">
         <v>140</v>
       </c>
@@ -1795,7 +1786,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:7" ht="13.2">
+    <row r="29" spans="1:6" ht="13.2">
       <c r="A29" s="4" t="s">
         <v>138</v>
       </c>
@@ -1807,7 +1798,7 @@
       <c r="E29" s="5"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:6" ht="15.6">
       <c r="A30" s="8">
         <v>7</v>
       </c>
@@ -1818,27 +1809,26 @@
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.2">
       <c r="A31" s="4" t="s">
         <v>136</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:7" ht="26.4">
+    <row r="32" spans="1:6" ht="26.4">
       <c r="A32" s="4" t="s">
         <v>134</v>
       </c>
@@ -1850,7 +1840,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="13.2">
+    <row r="33" spans="1:6" ht="13.2">
       <c r="A33" s="4" t="s">
         <v>132</v>
       </c>
@@ -1862,7 +1852,7 @@
       <c r="E33" s="5"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:7" ht="15.6">
+    <row r="34" spans="1:6" ht="15.6">
       <c r="A34" s="8">
         <v>8</v>
       </c>
@@ -1873,27 +1863,26 @@
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="13.2">
       <c r="A35" s="4" t="s">
         <v>130</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:7" ht="26.4">
+    <row r="36" spans="1:6" ht="26.4">
       <c r="A36" s="4" t="s">
         <v>128</v>
       </c>
@@ -1905,7 +1894,7 @@
       <c r="E36" s="5"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:7" ht="13.2">
+    <row r="37" spans="1:6" ht="13.2">
       <c r="A37" s="4" t="s">
         <v>126</v>
       </c>
@@ -1917,7 +1906,7 @@
       <c r="E37" s="5"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:7" ht="15.6">
+    <row r="38" spans="1:6" ht="15.6">
       <c r="A38" s="8">
         <v>9</v>
       </c>
@@ -1928,27 +1917,26 @@
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="13.2">
       <c r="A39" s="4" t="s">
         <v>124</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="26.4">
+    <row r="40" spans="1:6" ht="26.4">
       <c r="A40" s="4" t="s">
         <v>122</v>
       </c>
@@ -1960,7 +1948,7 @@
       <c r="E40" s="5"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:7" ht="13.2">
+    <row r="41" spans="1:6" ht="13.2">
       <c r="A41" s="4" t="s">
         <v>120</v>
       </c>
@@ -1972,7 +1960,7 @@
       <c r="E41" s="5"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:7" ht="15.6">
+    <row r="42" spans="1:6" ht="15.6">
       <c r="A42" s="8">
         <v>10</v>
       </c>
@@ -1985,25 +1973,24 @@
       <c r="F42" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="13.2">
+    </row>
+    <row r="43" spans="1:6" ht="13.2">
       <c r="A43" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:7" ht="13.2">
+    <row r="44" spans="1:6" ht="13.2">
       <c r="A44" s="4" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2002,7 @@
       <c r="E44" s="5"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="1:7" ht="13.2">
+    <row r="45" spans="1:6" ht="13.2">
       <c r="A45" s="4" t="s">
         <v>114</v>
       </c>
@@ -2027,7 +2014,7 @@
       <c r="E45" s="5"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="15.6">
+    <row r="46" spans="1:6" ht="15.6">
       <c r="A46" s="8">
         <v>11</v>
       </c>
@@ -2040,25 +2027,24 @@
       <c r="F46" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" ht="13.2">
+    </row>
+    <row r="47" spans="1:6" ht="13.2">
       <c r="A47" s="4" t="s">
         <v>112</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:7" ht="26.4">
+    <row r="48" spans="1:6" ht="26.4">
       <c r="A48" s="4" t="s">
         <v>110</v>
       </c>
@@ -2070,7 +2056,7 @@
       <c r="E48" s="5"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:7" ht="13.2">
+    <row r="49" spans="1:6" ht="13.2">
       <c r="A49" s="4" t="s">
         <v>108</v>
       </c>
@@ -2082,7 +2068,7 @@
       <c r="E49" s="5"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="1:7" ht="15.6">
+    <row r="50" spans="1:6" ht="15.6">
       <c r="A50" s="8">
         <v>12</v>
       </c>
@@ -2095,25 +2081,24 @@
       <c r="F50" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G50" s="6"/>
-    </row>
-    <row r="51" spans="1:7" ht="13.2">
+    </row>
+    <row r="51" spans="1:6" ht="13.2">
       <c r="A51" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="1:7" ht="26.4">
+    <row r="52" spans="1:6" ht="26.4">
       <c r="A52" s="4" t="s">
         <v>103</v>
       </c>
@@ -2125,7 +2110,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:7" ht="13.2">
+    <row r="53" spans="1:6" ht="13.2">
       <c r="A53" s="4" t="s">
         <v>101</v>
       </c>
@@ -2137,22 +2122,21 @@
       <c r="E53" s="5"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="1:7" ht="31.2">
+    <row r="54" spans="1:6" ht="31.2">
       <c r="A54" s="8">
         <v>13</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="19"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="6"/>
-    </row>
-    <row r="55" spans="1:7" ht="26.4">
+    </row>
+    <row r="55" spans="1:6" ht="26.4">
       <c r="A55" s="10" t="s">
         <v>99</v>
       </c>
@@ -2163,25 +2147,24 @@
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
       <c r="F55" s="16"/>
-      <c r="G55" s="9"/>
-    </row>
-    <row r="56" spans="1:7" ht="13.2">
+    </row>
+    <row r="56" spans="1:6" ht="13.2">
       <c r="A56" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="1:7" ht="13.2">
+    <row r="57" spans="1:6" ht="13.2">
       <c r="A57" s="4" t="s">
         <v>95</v>
       </c>
@@ -2193,7 +2176,7 @@
       <c r="E57" s="5"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="1:7" ht="13.2">
+    <row r="58" spans="1:6" ht="13.2">
       <c r="A58" s="4" t="s">
         <v>94</v>
       </c>
@@ -2205,7 +2188,7 @@
       <c r="E58" s="5"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="1:7" ht="15.6">
+    <row r="59" spans="1:6" ht="15.6">
       <c r="A59" s="8">
         <v>14</v>
       </c>
@@ -2218,25 +2201,24 @@
       <c r="F59" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G59" s="6"/>
-    </row>
-    <row r="60" spans="1:7" ht="13.2">
+    </row>
+    <row r="60" spans="1:6" ht="13.2">
       <c r="A60" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="1:7" ht="26.4">
+    <row r="61" spans="1:6" ht="26.4">
       <c r="A61" s="4" t="s">
         <v>90</v>
       </c>
@@ -2248,7 +2230,7 @@
       <c r="E61" s="5"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="1:7" ht="13.2">
+    <row r="62" spans="1:6" ht="13.2">
       <c r="A62" s="4" t="s">
         <v>88</v>
       </c>
@@ -2260,7 +2242,7 @@
       <c r="E62" s="5"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="1:7" ht="15.6">
+    <row r="63" spans="1:6" ht="15.6">
       <c r="A63" s="8">
         <v>15</v>
       </c>
@@ -2271,27 +2253,26 @@
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G63" s="6"/>
-    </row>
-    <row r="64" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="13.2">
       <c r="A64" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="1:7" ht="13.2">
+    <row r="65" spans="1:6" ht="13.2">
       <c r="A65" s="4" t="s">
         <v>84</v>
       </c>
@@ -2303,7 +2284,7 @@
       <c r="E65" s="5"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="1:7" ht="13.2">
+    <row r="66" spans="1:6" ht="13.2">
       <c r="A66" s="4" t="s">
         <v>82</v>
       </c>
@@ -2315,7 +2296,7 @@
       <c r="E66" s="5"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="1:7" ht="15.6">
+    <row r="67" spans="1:6" ht="15.6">
       <c r="A67" s="8">
         <v>16</v>
       </c>
@@ -2326,27 +2307,26 @@
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" s="6"/>
-    </row>
-    <row r="68" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="13.2">
       <c r="A68" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="1:7" ht="26.4">
+    <row r="69" spans="1:6" ht="26.4">
       <c r="A69" s="4" t="s">
         <v>78</v>
       </c>
@@ -2358,7 +2338,7 @@
       <c r="E69" s="5"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="1:7" ht="13.2">
+    <row r="70" spans="1:6" ht="13.2">
       <c r="A70" s="4" t="s">
         <v>76</v>
       </c>
@@ -2370,7 +2350,7 @@
       <c r="E70" s="5"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="1:7" ht="15.6">
+    <row r="71" spans="1:6" ht="15.6">
       <c r="A71" s="8">
         <v>17</v>
       </c>
@@ -2383,25 +2363,24 @@
       <c r="F71" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G71" s="6"/>
-    </row>
-    <row r="72" spans="1:7" ht="13.2">
+    </row>
+    <row r="72" spans="1:6" ht="13.2">
       <c r="A72" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="1:7" ht="26.4">
+    <row r="73" spans="1:6" ht="26.4">
       <c r="A73" s="4" t="s">
         <v>72</v>
       </c>
@@ -2413,7 +2392,7 @@
       <c r="E73" s="5"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="1:7" ht="13.2">
+    <row r="74" spans="1:6" ht="13.2">
       <c r="A74" s="4" t="s">
         <v>70</v>
       </c>
@@ -2425,7 +2404,7 @@
       <c r="E74" s="5"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="1:7" ht="15.6">
+    <row r="75" spans="1:6" ht="15.6">
       <c r="A75" s="8">
         <v>18</v>
       </c>
@@ -2436,27 +2415,26 @@
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G75" s="6"/>
-    </row>
-    <row r="76" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="13.2">
       <c r="A76" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="1:7" ht="26.4">
+    <row r="77" spans="1:6" ht="26.4">
       <c r="A77" s="4" t="s">
         <v>66</v>
       </c>
@@ -2468,7 +2446,7 @@
       <c r="E77" s="5"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="1:7" ht="13.2">
+    <row r="78" spans="1:6" ht="13.2">
       <c r="A78" s="4" t="s">
         <v>64</v>
       </c>
@@ -2480,7 +2458,7 @@
       <c r="E78" s="5"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="1:7" ht="15.6">
+    <row r="79" spans="1:6" ht="15.6">
       <c r="A79" s="8">
         <v>19</v>
       </c>
@@ -2491,27 +2469,26 @@
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G79" s="6"/>
-    </row>
-    <row r="80" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="13.2">
       <c r="A80" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" spans="1:7" ht="26.4">
+    <row r="81" spans="1:6" ht="26.4">
       <c r="A81" s="4" t="s">
         <v>59</v>
       </c>
@@ -2523,7 +2500,7 @@
       <c r="E81" s="5"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="1:7" ht="13.2">
+    <row r="82" spans="1:6" ht="13.2">
       <c r="A82" s="4" t="s">
         <v>59</v>
       </c>
@@ -2535,7 +2512,7 @@
       <c r="E82" s="5"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="1:7" ht="15.6">
+    <row r="83" spans="1:6" ht="15.6">
       <c r="A83" s="8">
         <v>20</v>
       </c>
@@ -2546,27 +2523,26 @@
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="6"/>
-    </row>
-    <row r="84" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="13.2">
       <c r="A84" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="1:7" ht="13.2">
+    <row r="85" spans="1:6" ht="13.2">
       <c r="A85" s="4" t="s">
         <v>55</v>
       </c>
@@ -2578,7 +2554,7 @@
       <c r="E85" s="5"/>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="1:7" ht="13.2">
+    <row r="86" spans="1:6" ht="13.2">
       <c r="A86" s="4" t="s">
         <v>53</v>
       </c>
@@ -2590,7 +2566,7 @@
       <c r="E86" s="5"/>
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="1:7" ht="15.6">
+    <row r="87" spans="1:6" ht="15.6">
       <c r="A87" s="8">
         <v>21</v>
       </c>
@@ -2601,27 +2577,26 @@
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="6"/>
-    </row>
-    <row r="88" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="13.2">
       <c r="A88" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E88" s="5"/>
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="1:7" ht="13.2">
+    <row r="89" spans="1:6" ht="13.2">
       <c r="A89" s="4" t="s">
         <v>49</v>
       </c>
@@ -2633,7 +2608,7 @@
       <c r="E89" s="5"/>
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="1:7" ht="13.2">
+    <row r="90" spans="1:6" ht="13.2">
       <c r="A90" s="4" t="s">
         <v>47</v>
       </c>
@@ -2645,7 +2620,7 @@
       <c r="E90" s="5"/>
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="1:7" ht="31.2">
+    <row r="91" spans="1:6" ht="31.2">
       <c r="A91" s="8">
         <v>22</v>
       </c>
@@ -2656,29 +2631,28 @@
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G91" s="6"/>
-    </row>
-    <row r="92" spans="1:7" ht="13.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="13.2">
       <c r="A92" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E92" s="18" t="s">
+      <c r="E92" s="20" t="s">
         <v>43</v>
       </c>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="1:7" ht="13.2">
+    <row r="93" spans="1:6" ht="13.2">
       <c r="A93" s="4" t="s">
         <v>42</v>
       </c>
@@ -2690,7 +2664,7 @@
       <c r="E93" s="16"/>
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="1:7" ht="13.2">
+    <row r="94" spans="1:6" ht="13.2">
       <c r="A94" s="4" t="s">
         <v>40</v>
       </c>
@@ -2702,7 +2676,7 @@
       <c r="E94" s="16"/>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="1:7" ht="15.6">
+    <row r="95" spans="1:6" ht="15.6">
       <c r="A95" s="8">
         <v>23</v>
       </c>
@@ -2713,27 +2687,26 @@
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
       <c r="F95" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="6"/>
-    </row>
-    <row r="96" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="13.2">
       <c r="A96" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="1:7" ht="13.2">
+    <row r="97" spans="1:6" ht="13.2">
       <c r="A97" s="4" t="s">
         <v>36</v>
       </c>
@@ -2745,7 +2718,7 @@
       <c r="E97" s="5"/>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="1:7" ht="13.2">
+    <row r="98" spans="1:6" ht="13.2">
       <c r="A98" s="4" t="s">
         <v>34</v>
       </c>
@@ -2757,7 +2730,7 @@
       <c r="E98" s="5"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="1:7" ht="13.2">
+    <row r="99" spans="1:6" ht="13.2">
       <c r="A99" s="4" t="s">
         <v>33</v>
       </c>
@@ -2769,7 +2742,7 @@
       <c r="E99" s="5"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="1:7" ht="15.6">
+    <row r="100" spans="1:6" ht="15.6">
       <c r="A100" s="8">
         <v>24</v>
       </c>
@@ -2782,25 +2755,24 @@
       <c r="F100" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G100" s="6"/>
-    </row>
-    <row r="101" spans="1:7" ht="13.2">
+    </row>
+    <row r="101" spans="1:6" ht="13.2">
       <c r="A101" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D101" s="17" t="s">
+      <c r="D101" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E101" s="5"/>
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="1:7" ht="13.2">
+    <row r="102" spans="1:6" ht="13.2">
       <c r="A102" s="4" t="s">
         <v>28</v>
       </c>
@@ -2812,7 +2784,7 @@
       <c r="E102" s="5"/>
       <c r="F102" s="2"/>
     </row>
-    <row r="103" spans="1:7" ht="13.2">
+    <row r="103" spans="1:6" ht="13.2">
       <c r="A103" s="4" t="s">
         <v>26</v>
       </c>
@@ -2824,7 +2796,7 @@
       <c r="E103" s="5"/>
       <c r="F103" s="2"/>
     </row>
-    <row r="104" spans="1:7" ht="15.6">
+    <row r="104" spans="1:6" ht="15.6">
       <c r="A104" s="8">
         <v>25</v>
       </c>
@@ -2835,29 +2807,28 @@
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
       <c r="F104" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G104" s="6"/>
-    </row>
-    <row r="105" spans="1:7" ht="13.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="13.2">
       <c r="A105" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E105" s="18" t="s">
+      <c r="E105" s="20" t="s">
         <v>22</v>
       </c>
       <c r="F105" s="2"/>
     </row>
-    <row r="106" spans="1:7" ht="13.2">
+    <row r="106" spans="1:6" ht="13.2">
       <c r="A106" s="4" t="s">
         <v>21</v>
       </c>
@@ -2869,7 +2840,7 @@
       <c r="E106" s="16"/>
       <c r="F106" s="2"/>
     </row>
-    <row r="107" spans="1:7" ht="13.2">
+    <row r="107" spans="1:6" ht="13.2">
       <c r="A107" s="4" t="s">
         <v>19</v>
       </c>
@@ -2881,7 +2852,7 @@
       <c r="E107" s="16"/>
       <c r="F107" s="2"/>
     </row>
-    <row r="108" spans="1:7" ht="15.6">
+    <row r="108" spans="1:6" ht="15.6">
       <c r="A108" s="8">
         <v>26</v>
       </c>
@@ -2894,25 +2865,24 @@
       <c r="F108" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G108" s="6"/>
-    </row>
-    <row r="109" spans="1:7" ht="13.2">
+    </row>
+    <row r="109" spans="1:6" ht="13.2">
       <c r="A109" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D109" s="17" t="s">
+      <c r="D109" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E109" s="5"/>
       <c r="F109" s="2"/>
     </row>
-    <row r="110" spans="1:7" ht="26.4">
+    <row r="110" spans="1:6" ht="26.4">
       <c r="A110" s="4" t="s">
         <v>13</v>
       </c>
@@ -2924,7 +2894,7 @@
       <c r="E110" s="5"/>
       <c r="F110" s="2"/>
     </row>
-    <row r="111" spans="1:7" ht="13.2">
+    <row r="111" spans="1:6" ht="13.2">
       <c r="A111" s="4" t="s">
         <v>11</v>
       </c>
@@ -2936,7 +2906,7 @@
       <c r="E111" s="5"/>
       <c r="F111" s="2"/>
     </row>
-    <row r="112" spans="1:7" ht="15.6">
+    <row r="112" spans="1:6" ht="15.6">
       <c r="A112" s="8">
         <v>27</v>
       </c>
@@ -2949,7 +2919,6 @@
       <c r="F112" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G112" s="6"/>
     </row>
     <row r="113" spans="1:6" ht="13.2">
       <c r="A113" s="4" t="s">
@@ -2958,13 +2927,13 @@
       <c r="B113" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D113" s="17" t="s">
+      <c r="D113" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E113" s="18" t="s">
+      <c r="E113" s="20" t="s">
         <v>4</v>
       </c>
       <c r="F113" s="2"/>
@@ -3100,45 +3069,6 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="D113:D115"/>
     <mergeCell ref="E113:E115"/>
     <mergeCell ref="C76:C78"/>
     <mergeCell ref="D76:D78"/>
@@ -3155,10 +3085,49 @@
     <mergeCell ref="C92:C94"/>
     <mergeCell ref="C109:C111"/>
     <mergeCell ref="D109:D111"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
     <mergeCell ref="C96:C99"/>
     <mergeCell ref="D96:D99"/>
     <mergeCell ref="C101:C103"/>
     <mergeCell ref="D101:D103"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D47:D49"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D53 F24 F27:F29 F31 F33:F34 F36:F38 F40:F50 F52:F54 D56:D115 F57:F115">
